--- a/updated_geospatialdata_evaluation.xlsx
+++ b/updated_geospatialdata_evaluation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PHD\PLUS-CLIMB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F248E60-C77A-4511-9A4E-5B53A341E43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D4E374-5224-40B8-BEF9-06E00C264629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="195">
   <si>
     <t>Title</t>
   </si>
@@ -554,21 +554,6 @@
     <t>CHIRPS</t>
   </si>
   <si>
-    <t>Dataset</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Strengths</t>
-  </si>
-  <si>
-    <t>Applications</t>
-  </si>
-  <si>
-    <t>Link</t>
-  </si>
-  <si>
     <t>CHIRPS v3</t>
   </si>
   <si>
@@ -615,6 +600,15 @@
   </si>
   <si>
     <t>Aerospace Information Research Institute,</t>
+  </si>
+  <si>
+    <t>Night Time Lights Data</t>
+  </si>
+  <si>
+    <t>AEZ classification by climate, soil, terrain, land cover - GAEZ v5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.apps.fao.org/gaez/?lang=en </t>
   </si>
 </sst>
 </file>
@@ -684,7 +678,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -693,15 +687,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1679,7 +1674,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65084144-70D3-4422-8FAA-11399B9A7013}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.33203125" customWidth="1"/>
@@ -1764,7 +1759,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>124</v>
       </c>
@@ -1855,75 +1850,43 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1</v>
+        <v>191</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>3</v>
+        <v>185</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>5</v>
+        <v>187</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>189</v>
+      <c r="K6" s="5" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" xr:uid="{7040D226-8DF3-4517-9BD9-2BD3B5F5B250}"/>
     <hyperlink ref="K5" r:id="rId2" xr:uid="{17411A7A-7221-4612-8E74-D18FAE465D3D}"/>
-    <hyperlink ref="K7" r:id="rId3" xr:uid="{EEB6A1B8-5133-4F59-B1F7-B6F9B82BDBD9}"/>
+    <hyperlink ref="K6" r:id="rId3" xr:uid="{EEB6A1B8-5133-4F59-B1F7-B6F9B82BDBD9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1942,40 +1905,41 @@
     <col min="7" max="7" width="21" customWidth="1"/>
     <col min="8" max="8" width="18.109375" customWidth="1"/>
     <col min="9" max="9" width="23.88671875" customWidth="1"/>
+    <col min="11" max="11" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:11" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2350,48 +2314,50 @@
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+    <row r="13" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="K14" s="6" t="s">
+      <c r="K13" s="5" t="s">
         <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -2403,7 +2369,8 @@
     <hyperlink ref="K10" r:id="rId5" xr:uid="{EE2D1CF5-0567-4005-B56C-D04C4D6CEBDB}"/>
     <hyperlink ref="K11" r:id="rId6" xr:uid="{972172CA-939B-4820-9D68-C1D6981759E9}"/>
     <hyperlink ref="K12" r:id="rId7" xr:uid="{64931B84-A14A-49E7-A652-594DB38EDA0F}"/>
-    <hyperlink ref="K14" r:id="rId8" display="https://www.chc.ucsb.edu/data/chirps" xr:uid="{CC261FCE-DDE3-4E1C-A649-B951D950502F}"/>
+    <hyperlink ref="K13" r:id="rId8" display="https://www.chc.ucsb.edu/data/chirps" xr:uid="{CC261FCE-DDE3-4E1C-A649-B951D950502F}"/>
+    <hyperlink ref="K14" r:id="rId9" xr:uid="{BD2D1F2E-3A4C-4C07-A9C2-C6B5AD945700}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2411,7 +2378,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A87789C-E519-4DC2-AEB1-61A7221145E6}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.44140625" customWidth="1"/>
@@ -2636,6 +2603,11 @@
         <v>122</v>
       </c>
     </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" xr:uid="{57E34B00-C932-484E-B0D5-5B242CD2DCB7}"/>
